--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484812_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484812_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1555</v>
+        <v>6.2504</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2183</v>
+        <v>6.472</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.2216</v>
       </c>
       <c r="G2" t="n">
         <v>5.9081</v>
@@ -610,13 +610,13 @@
         <v>2.6418</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.0545</v>
+        <v>-1.9596</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1975</v>
+        <v>-0.9439</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.857</v>
+        <v>-1.0157</v>
       </c>
       <c r="V2" t="n">
         <v>0.6036</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. GALVEZ ARROYO</t>
+          <t>N. ALBALADEJO PEREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1911</v>
+        <v>1.4974</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6831</v>
+        <v>2.0964</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.492</v>
+        <v>-0.599</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2445</v>
+        <v>1.3321</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2717</v>
+        <v>1.9471</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9728</v>
+        <v>-0.615</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7451</v>
+        <v>2.5034</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9637</v>
+        <v>3.7032</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7815</v>
+        <v>-1.1998</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5006</v>
+        <v>-1.1713</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6919</v>
+        <v>-1.7561</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1913</v>
+        <v>0.5849</v>
       </c>
       <c r="P3" t="n">
-        <v>1.887</v>
+        <v>1.3209</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8305</v>
+        <v>2.2644</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7518</v>
+        <v>-0.8539</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6655</v>
+        <v>-0.7087</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0862</v>
+        <v>-0.1451</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.1886</v>
+        <v>-0.3018</v>
       </c>
       <c r="W3" t="n">
-        <v>1.547</v>
+        <v>1.2452</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.7356</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. ALBALADEJO PEREZ</t>
+          <t>V. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0909</v>
+        <v>1.0815</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9015</v>
+        <v>3.547</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8107</v>
+        <v>-2.4655</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3321</v>
+        <v>3.2445</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9471</v>
+        <v>1.2717</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.615</v>
+        <v>1.9728</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5034</v>
+        <v>3.7451</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7032</v>
+        <v>2.9637</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1998</v>
+        <v>0.7815</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1713</v>
+        <v>-0.5006</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7561</v>
+        <v>-1.6919</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5849</v>
+        <v>1.1913</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3209</v>
+        <v>1.887</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2644</v>
+        <v>2.8305</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2604</v>
+        <v>-1.8614</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9036</v>
+        <v>-0.8016</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3568</v>
+        <v>-1.0598</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3018</v>
+        <v>-2.1886</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2452</v>
+        <v>1.547</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.547</v>
+        <v>-3.7356</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5587</v>
+        <v>0.6116</v>
       </c>
       <c r="E5" t="n">
         <v>-0.2121</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7708</v>
+        <v>0.8237</v>
       </c>
       <c r="G5" t="n">
         <v>0.5945</v>
@@ -844,13 +844,13 @@
         <v>0.3774</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4133</v>
+        <v>-0.3603</v>
       </c>
       <c r="T5" t="n">
         <v>-0.0929</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3204</v>
+        <v>-0.2674</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.5712</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0119</v>
+        <v>0.0469</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5507</v>
+        <v>0.5243</v>
       </c>
       <c r="G6" t="n">
         <v>0.7822</v>
@@ -922,13 +922,13 @@
         <v>0.3774</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6207</v>
+        <v>-0.5884</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1176</v>
+        <v>-0.0588</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5032</v>
+        <v>-0.5296</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. SEVERA LENCINA</t>
+          <t>S. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.032</v>
+        <v>-0.9126</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1584</v>
+        <v>1.4028</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1264</v>
+        <v>-2.3154</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.4475</v>
+        <v>3.6165</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5790999999999999</v>
+        <v>0.1902</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8684</v>
+        <v>3.4263</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.6563</v>
+        <v>4.751</v>
       </c>
       <c r="K7" t="n">
-        <v>0.169</v>
+        <v>2.2562</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8253</v>
+        <v>2.4948</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7913</v>
+        <v>-1.1345</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7482</v>
+        <v>-2.066</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0431</v>
+        <v>0.9315</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7548</v>
+        <v>2.8305</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6607</v>
+        <v>-2.3595</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4979</v>
+        <v>-1.1404</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1629</v>
+        <v>-1.2191</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.1696</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.7922</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. GALVEZ ARROYO</t>
+          <t>C. SEVERA LENCINA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2372</v>
+        <v>-1.4746</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0517</v>
+        <v>-1.5481</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2889</v>
+        <v>0.0735</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6165</v>
+        <v>-2.4475</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1902</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4263</v>
+        <v>-1.8684</v>
       </c>
       <c r="J8" t="n">
-        <v>4.751</v>
+        <v>-1.6563</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2562</v>
+        <v>0.169</v>
       </c>
       <c r="L8" t="n">
-        <v>2.4948</v>
+        <v>-1.8253</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1345</v>
+        <v>-0.7913</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.066</v>
+        <v>-0.7482</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9315</v>
+        <v>-0.0431</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.7548</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8305</v>
+        <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.6841</v>
+        <v>0.2181</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.4915</v>
+        <v>0.1081</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1926</v>
+        <v>0.11</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1696</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7922</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8271</v>
+        <v>-2.1375</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1759</v>
+        <v>-0.5656</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6513</v>
+        <v>-1.5719</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1836</v>
@@ -1156,13 +1156,13 @@
         <v>0.7548</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1487</v>
+        <v>-0.1617</v>
       </c>
       <c r="T9" t="n">
-        <v>0.238</v>
+        <v>-0.1517</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0893</v>
+        <v>-0.01</v>
       </c>
       <c r="V9" t="n">
         <v>-1.547</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.9073</v>
+        <v>-6.662</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2662</v>
+        <v>-3.9151</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6411</v>
+        <v>-2.747</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2651</v>
@@ -1234,13 +1234,13 @@
         <v>2.2644</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1709</v>
+        <v>-1.9256</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1264</v>
+        <v>-0.7753</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0445</v>
+        <v>-1.1503</v>
       </c>
       <c r="V10" t="n">
         <v>-2.7922</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4686</v>
+        <v>-1.174600000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>7.030100000000002</v>
+        <v>7.324200000000002</v>
       </c>
       <c r="F11" t="n">
         <v>-8.498899999999999</v>
@@ -1279,7 +1279,7 @@
         <v>8.5817</v>
       </c>
       <c r="H11" t="n">
-        <v>5.767800000000001</v>
+        <v>5.7678</v>
       </c>
       <c r="I11" t="n">
         <v>2.813999999999999</v>
@@ -1291,7 +1291,7 @@
         <v>15.4483</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.142599999999999</v>
+        <v>-3.1426</v>
       </c>
       <c r="M11" t="n">
         <v>-3.724</v>
@@ -1300,7 +1300,7 @@
         <v>-9.680499999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>5.9567</v>
+        <v>5.956700000000001</v>
       </c>
       <c r="P11" t="n">
         <v>8.4915</v>
@@ -1312,19 +1312,19 @@
         <v>15.096</v>
       </c>
       <c r="S11" t="n">
-        <v>-10.1463</v>
+        <v>-9.8523</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.8591</v>
+        <v>-4.5652</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.287100000000001</v>
+        <v>-5.287000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-8.3956</v>
       </c>
       <c r="W11" t="n">
-        <v>6.188000000000001</v>
+        <v>6.188</v>
       </c>
       <c r="X11" t="n">
         <v>-14.5836</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. MARCO CLIMENT</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.9503</v>
+        <v>3.9827</v>
       </c>
       <c r="E12" t="n">
-        <v>5.1335</v>
+        <v>3.301</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1832</v>
+        <v>0.6817</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0038</v>
+        <v>2.4148</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0736</v>
+        <v>0.2238</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0697</v>
+        <v>2.1909</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3102</v>
+        <v>2.7193</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2194</v>
+        <v>1.3946</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09080000000000001</v>
+        <v>1.3247</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.314</v>
+        <v>-0.3045</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.293</v>
+        <v>-1.1708</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.021</v>
+        <v>0.8663</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.2079</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.1514</v>
+        <v>-0.9435</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9435</v>
+        <v>0.5661</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1208</v>
+        <v>0.7719</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5599</v>
+        <v>-0.0218</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5609</v>
+        <v>0.7936</v>
       </c>
       <c r="V12" t="n">
-        <v>3.0413</v>
+        <v>1.1735</v>
       </c>
       <c r="W12" t="n">
-        <v>3.4148</v>
+        <v>1.547</v>
       </c>
       <c r="X12" t="n">
         <v>-0.3736</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5593</v>
+        <v>3.2298</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7192</v>
+        <v>3.5243</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1598</v>
+        <v>-0.2945</v>
       </c>
       <c r="G13" t="n">
         <v>2.1294</v>
@@ -1468,13 +1468,13 @@
         <v>0.3774</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6148</v>
+        <v>1.2853</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.6463</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.639</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3736</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>F. MARCO CLIMENT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2561</v>
+        <v>2.8424</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9113</v>
+        <v>3.4771</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3448</v>
+        <v>-0.6347</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4148</v>
+        <v>-0.0038</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2238</v>
+        <v>-0.0736</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1909</v>
+        <v>0.0697</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7193</v>
+        <v>2.3102</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3946</v>
+        <v>2.2194</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3247</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3045</v>
+        <v>-2.314</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1708</v>
+        <v>-2.293</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8663</v>
+        <v>-0.021</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3774</v>
+        <v>-3.2079</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9435</v>
+        <v>-4.1514</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0453</v>
+        <v>3.0128</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4115</v>
+        <v>1.9035</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4568</v>
+        <v>1.1093</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1735</v>
+        <v>3.0413</v>
       </c>
       <c r="W14" t="n">
-        <v>1.547</v>
+        <v>3.4148</v>
       </c>
       <c r="X14" t="n">
         <v>-0.3736</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3702</v>
+        <v>2.5265</v>
       </c>
       <c r="E15" t="n">
         <v>2.2622</v>
       </c>
       <c r="F15" t="n">
-        <v>0.108</v>
+        <v>0.2643</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5153</v>
@@ -1624,13 +1624,13 @@
         <v>0.5661</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1711</v>
+        <v>-0.0147</v>
       </c>
       <c r="T15" t="n">
         <v>-0.3527</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1817</v>
+        <v>0.338</v>
       </c>
       <c r="V15" t="n">
         <v>2.4904</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. CERVANTES GUERRA</t>
+          <t>P. ANTICH MINGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.78</v>
+        <v>1.5103</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3602</v>
+        <v>1.4841</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4197</v>
+        <v>0.0262</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4779</v>
+        <v>-1.5445</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3343</v>
+        <v>-0.2348</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8122</v>
+        <v>-1.3096</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8276</v>
+        <v>0.3955</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4703</v>
+        <v>1.5542</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3573</v>
+        <v>-1.1587</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3497</v>
+        <v>-1.9399</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8047</v>
+        <v>-1.789</v>
       </c>
       <c r="O16" t="n">
-        <v>0.455</v>
+        <v>-0.1509</v>
       </c>
       <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-1.1322</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-1.887</v>
-      </c>
       <c r="R16" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7171</v>
+        <v>2.1831</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4196</v>
+        <v>0.9756</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2975</v>
+        <v>1.2075</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2828</v>
+        <v>0.8716</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2828</v>
+        <v>-0.3736</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>L. CERVANTES GUERRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2654</v>
+        <v>1.0295</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9969</v>
+        <v>0.7756</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7315</v>
+        <v>0.2539</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5445</v>
+        <v>0.4779</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2348</v>
+        <v>-1.3343</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3096</v>
+        <v>1.8122</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3955</v>
+        <v>1.8276</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5542</v>
+        <v>0.4703</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1587</v>
+        <v>1.3573</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9399</v>
+        <v>-1.3497</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.789</v>
+        <v>-1.8047</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1509</v>
+        <v>0.455</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1322</v>
+        <v>-1.887</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1322</v>
+        <v>0.7548</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9382</v>
+        <v>1.9667</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4884</v>
+        <v>0.835</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4498</v>
+        <v>1.1317</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8716</v>
+        <v>-0.2828</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3736</v>
+        <v>-0.2828</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4465</v>
+        <v>-0.8482</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08790000000000001</v>
+        <v>-0.4968</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5343</v>
+        <v>-0.3515</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4823</v>
@@ -1858,13 +1858,13 @@
         <v>0.7548</v>
       </c>
       <c r="S18" t="n">
-        <v>2.2438</v>
+        <v>1.842</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7876</v>
+        <v>1.203</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4562</v>
+        <v>0.639</v>
       </c>
       <c r="V18" t="n">
         <v>1.2452</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7525</v>
+        <v>-1.6286</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0323</v>
+        <v>-0.9348</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.6938</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4051</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1587</v>
+        <v>-0.0348</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2352</v>
+        <v>-0.1377</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0764</v>
+        <v>0.1029</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2763</v>
+        <v>-2.1524</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3673</v>
+        <v>-1.2699</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.909</v>
+        <v>-0.8825</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9266</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2175</v>
+        <v>-0.0936</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2352</v>
+        <v>-0.1377</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. FONT FENOLLAR</t>
+          <t>P. LUENGO MATEO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8895</v>
+        <v>-3.0045</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6744</v>
+        <v>-1.3392</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2151</v>
+        <v>-1.6653</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3741</v>
+        <v>-5.352</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7935</v>
+        <v>-3.0998</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5805</v>
+        <v>-2.2522</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.8642</v>
+        <v>-3.265</v>
       </c>
       <c r="K21" t="n">
-        <v>0.08450000000000001</v>
+        <v>-0.6441</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9487</v>
+        <v>-2.6209</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5099</v>
+        <v>-2.0871</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8781</v>
+        <v>-2.4558</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3682</v>
+        <v>0.3687</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1322</v>
+        <v>0.3774</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.887</v>
+        <v>-0.3774</v>
       </c>
       <c r="R21" t="n">
         <v>0.7548</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3833</v>
+        <v>1.74</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4703</v>
+        <v>0.4543</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08699999999999999</v>
+        <v>1.2857</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2301</v>
       </c>
       <c r="W21" t="n">
-        <v>1.547</v>
+        <v>1.8488</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.547</v>
+        <v>-1.6188</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. LUENGO MATEO</t>
+          <t>A. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3477</v>
+        <v>-3.4204</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8982</v>
+        <v>-2.2847</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4495</v>
+        <v>-1.1357</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.352</v>
+        <v>-2.3741</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.0998</v>
+        <v>-0.7935</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2522</v>
+        <v>-1.5805</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.265</v>
+        <v>-1.8642</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6441</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.6209</v>
+        <v>-1.9487</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0871</v>
+        <v>-0.5099</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.4558</v>
+        <v>-0.8781</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3687</v>
+        <v>0.3682</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3774</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.3774</v>
+        <v>-1.887</v>
       </c>
       <c r="R22" t="n">
         <v>0.7548</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6031</v>
+        <v>0.0858</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1046</v>
+        <v>-0.0806</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.1664</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2301</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8488</v>
+        <v>1.547</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6188</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4688</v>
+        <v>4.067100000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>8.498999999999999</v>
+        <v>8.498900000000003</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.030200000000001</v>
+        <v>-4.4319</v>
       </c>
       <c r="G23" t="n">
         <v>-8.5816</v>
@@ -2221,7 +2221,7 @@
         <v>-2.814</v>
       </c>
       <c r="J23" t="n">
-        <v>3.724000000000001</v>
+        <v>3.724</v>
       </c>
       <c r="K23" t="n">
         <v>9.6806</v>
@@ -2248,16 +2248,16 @@
         <v>6.604500000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>10.1463</v>
+        <v>12.7445</v>
       </c>
       <c r="T23" t="n">
         <v>5.2872</v>
       </c>
       <c r="U23" t="n">
-        <v>4.8591</v>
+        <v>7.457200000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>8.3957</v>
+        <v>8.395700000000001</v>
       </c>
       <c r="W23" t="n">
         <v>14.5836</v>
